--- a/ASM.xlsx
+++ b/ASM.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20252" uniqueCount="6212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20381" uniqueCount="6239">
   <si>
     <t>İl</t>
   </si>
@@ -18650,6 +18650,87 @@
   </si>
   <si>
     <t>İSTANBUL ÜSKÜDAR 179 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL SANCAKTEPE AYHAN-H. CAHİT GÜLAN AİLE SAĞLIĞI MERKEZİ</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>İSTANBUL TUZLA 095 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL SANCAKTEPE 156 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL SANCAKTEPE 155 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL SANCAKTEPE 153 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL MALTEPE 178 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL EYÜPSULTAN 128 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ESENYURT149 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ESENYURT148 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ESENYURT140 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ESENYURT 233 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ESENLER 067 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BEYLİKDÜZÜ 123 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAYRAMPAŞA 098 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAKIRKÖY 061 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAHÇELİEVLER 211 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAHÇELİEVLER 210 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ARNAVUTKÖY 109 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ARNAVUTKÖY 110 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ARNAVUTKÖY 111 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ATAŞEHİR 145 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ATAŞEHİR 146 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ATAŞEHİR 147 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL ATAŞEHİR 148 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAHÇELİEVLER 208 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
+  </si>
+  <si>
+    <t>İSTANBUL BAHÇELİEVLER 209 NOLU AİLE HEKİMLİĞİ BİRİMİ</t>
   </si>
 </sst>
 </file>
@@ -18705,11 +18786,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19014,11 +19096,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5063"/>
+  <dimension ref="A1:D5096"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.85546875"/>
-    <col min="3" max="3" width="55.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.7109375" customWidth="1"/>
     <col min="4" max="4" width="92.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -89904,7 +89986,461 @@
         <v>6210</v>
       </c>
     </row>
+    <row r="5064" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5064" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5064" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5064" t="s">
+        <v>6230</v>
+      </c>
+      <c r="D5064" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5065" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5065" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5065" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5065" t="s">
+        <v>6231</v>
+      </c>
+      <c r="D5065" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5066" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5066" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5066" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5066" t="s">
+        <v>6232</v>
+      </c>
+      <c r="D5066" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5067" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5067" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5067" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5067" t="s">
+        <v>6233</v>
+      </c>
+      <c r="D5067" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5068" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5068" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5068" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5068" t="s">
+        <v>6234</v>
+      </c>
+      <c r="D5068" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5069" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5069" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5069" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5069" t="s">
+        <v>6235</v>
+      </c>
+      <c r="D5069" t="s">
+        <v>6202</v>
+      </c>
+    </row>
+    <row r="5070" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5070" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5070" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5070" t="s">
+        <v>6236</v>
+      </c>
+      <c r="D5070" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5071" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5071" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5071" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5071" t="s">
+        <v>6237</v>
+      </c>
+      <c r="D5071" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="5072" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5072" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5072" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5072" t="s">
+        <v>6238</v>
+      </c>
+      <c r="D5072" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="5073" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5073" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5073" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5073" t="s">
+        <v>6229</v>
+      </c>
+      <c r="D5073" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="5074" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5074" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5074" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5074" t="s">
+        <v>6228</v>
+      </c>
+      <c r="D5074" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="5075" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5075" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5075" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C5075" t="s">
+        <v>6227</v>
+      </c>
+      <c r="D5075" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5076" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5076" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C5076" t="s">
+        <v>6226</v>
+      </c>
+      <c r="D5076" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="5077" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5077" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5077" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C5077" t="s">
+        <v>6225</v>
+      </c>
+      <c r="D5077" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5078" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5078" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C5078" t="s">
+        <v>6224</v>
+      </c>
+      <c r="D5078" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5079" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5079" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C5079" t="s">
+        <v>6223</v>
+      </c>
+      <c r="D5079" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5080" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5080" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C5080" t="s">
+        <v>6222</v>
+      </c>
+      <c r="D5080" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5081" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5081" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C5081" t="s">
+        <v>6221</v>
+      </c>
+      <c r="D5081" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5082" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5082" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C5082" t="s">
+        <v>6220</v>
+      </c>
+      <c r="D5082" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5083" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5083" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C5083" t="s">
+        <v>6219</v>
+      </c>
+      <c r="D5083" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5084" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5084" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5084" t="s">
+        <v>3810</v>
+      </c>
+      <c r="D5084" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="5085" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5085" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5085" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5085" t="s">
+        <v>3812</v>
+      </c>
+      <c r="D5085" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5086" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5086" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5086" t="s">
+        <v>3803</v>
+      </c>
+      <c r="D5086" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5087" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5087" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5087" t="s">
+        <v>3804</v>
+      </c>
+      <c r="D5087" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5088" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5088" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5088" t="s">
+        <v>3813</v>
+      </c>
+      <c r="D5088" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5089" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5089" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5089" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D5089" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5090" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5090" t="s">
+        <v>3767</v>
+      </c>
+      <c r="C5090" t="s">
+        <v>4047</v>
+      </c>
+      <c r="D5090" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5091" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5091" t="s">
+        <v>4064</v>
+      </c>
+      <c r="C5091" t="s">
+        <v>6218</v>
+      </c>
+      <c r="D5091" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="5092" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5092" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5092" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C5092" t="s">
+        <v>6217</v>
+      </c>
+      <c r="D5092" t="s">
+        <v>6212</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5093" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5093" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C5093" t="s">
+        <v>6216</v>
+      </c>
+      <c r="D5093" t="s">
+        <v>6212</v>
+      </c>
+    </row>
+    <row r="5094" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5094" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5094" t="s">
+        <v>4567</v>
+      </c>
+      <c r="C5094" t="s">
+        <v>6215</v>
+      </c>
+      <c r="D5094" t="s">
+        <v>4601</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5095" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5095" t="s">
+        <v>5474</v>
+      </c>
+      <c r="C5095" s="2" t="s">
+        <v>6214</v>
+      </c>
+      <c r="D5095" t="s">
+        <v>5508</v>
+      </c>
+    </row>
+    <row r="5096" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C5096" s="2" t="s">
+        <v>6213</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>